--- a/PPG/Discentes.xlsx
+++ b/PPG/Discentes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arthurferreira/Google Drive - arthur_sf/Observatorios/ObservatorioUNISUAM-CR/PPG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7D8F640-889C-5442-AE91-2FC88812D788}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47B4D033-5F5E-9E41-B1EC-118B09CB0CEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="880" yWindow="660" windowWidth="29360" windowHeight="18940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="920" yWindow="660" windowWidth="29320" windowHeight="18940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Discentes" sheetId="9" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3597" uniqueCount="769">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3598" uniqueCount="769">
   <si>
     <t>Pré-inscrito</t>
   </si>
@@ -15664,9 +15664,11 @@
         <v>677</v>
       </c>
       <c r="D585" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="E585" s="6"/>
+        <v>2</v>
+      </c>
+      <c r="E585" s="6">
+        <v>46239</v>
+      </c>
       <c r="F585" s="10" t="s">
         <v>13</v>
       </c>
@@ -16456,9 +16458,11 @@
         <v>696</v>
       </c>
       <c r="D623" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="E623" s="6"/>
+        <v>2</v>
+      </c>
+      <c r="E623" s="6">
+        <v>46287</v>
+      </c>
       <c r="F623" s="10" t="s">
         <v>33</v>
       </c>
@@ -17189,9 +17193,11 @@
         <v>45852</v>
       </c>
       <c r="D658" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="E658" s="6"/>
+        <v>2</v>
+      </c>
+      <c r="E658" s="6">
+        <v>46268</v>
+      </c>
       <c r="F658" s="10" t="s">
         <v>13</v>
       </c>
@@ -18115,11 +18121,15 @@
         <v>46077</v>
       </c>
       <c r="D707" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="E707" s="6"/>
+        <v>2</v>
+      </c>
+      <c r="E707" s="6">
+        <v>46269</v>
+      </c>
       <c r="F707" s="10"/>
-      <c r="G707" s="10"/>
+      <c r="G707" s="10" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="708" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A708" s="10" t="s">
